--- a/output/pdf_financials_xlsx/CEMX.xlsx
+++ b/output/pdf_financials_xlsx/CEMX.xlsx
@@ -1174,19 +1174,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>19.945</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>10.682</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.288</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>10.295</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>11.942</v>
       </c>
     </row>
     <row r="35">
@@ -1218,19 +1218,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>19.945</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>10.682</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>3.288</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>10.295</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>11.942</v>
       </c>
     </row>
     <row r="37">
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>20.808</v>
+        <v>0.863</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.532</v>
@@ -1494,7 +1494,7 @@
         <v>0.591</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>12.393</v>
+        <v>0.451</v>
       </c>
     </row>
     <row r="49">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">

--- a/output/pdf_financials_xlsx/CEMX.xlsx
+++ b/output/pdf_financials_xlsx/CEMX.xlsx
@@ -2887,16 +2887,16 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.134</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -7445,7 +7445,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -9465,7 +9469,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -10656,7 +10664,11 @@
           <t>Proceeds on sale of property and equipment (note 8)</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E177" s="5" t="n">
         <v>0.055</v>
       </c>

--- a/output/pdf_financials_xlsx/CEMX.xlsx
+++ b/output/pdf_financials_xlsx/CEMX.xlsx
@@ -1306,19 +1306,19 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="41">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>4.911</v>
+        <v>4.931</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>7.337</v>
+        <v>7.348</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>12.865</v>
+        <v>12.919</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>6.742</v>
+        <v>6.754</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>11.677</v>
+        <v>11.689</v>
       </c>
     </row>
     <row r="42">
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.863</v>
+        <v>0.843</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.532</v>
@@ -1494,7 +1494,7 @@
         <v>0.591</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.451</v>
+        <v>0.439</v>
       </c>
     </row>
     <row r="49">
@@ -1976,19 +1976,19 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.578</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.729</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="71">
@@ -1998,19 +1998,19 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0.877</v>
+        <v>1.455</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0.9370000000000001</v>
+        <v>1.527</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.915</v>
+        <v>1.644</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.995</v>
+        <v>1.755</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="72">
@@ -2086,19 +2086,19 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.578</v>
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>4.089</v>
+        <v>3.499</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.729</v>
+        <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>1.052</v>
+        <v>0.324</v>
       </c>
     </row>
     <row r="76">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>0</v>
+        <v>1.106</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>0</v>
+        <v>0.574</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>0</v>
+        <v>1.725</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="79">
@@ -2174,19 +2174,19 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>2.726</v>
+        <v>3.832</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>1.975</v>
+        <v>2.549</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>1.014</v>
+        <v>1.6</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>0.108</v>
+        <v>1.833</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="80">
@@ -2196,21 +2196,19 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>0.11408758430702</v>
+        <v>0.1674107849656439</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.1049671977507029</v>
+        <v>0.1469252397087449</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.06715872297461964</v>
+        <v>0.1129408487971312</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.02951249531760047</v>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.09600256863059881</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.05327474263707507</v>
       </c>
     </row>
     <row r="81">
@@ -2308,19 +2306,19 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>4.213</v>
+        <v>3.107</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>0.574</v>
+        <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>1.725</v>
+        <v>0</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>2.375</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="86">
@@ -3406,7 +3404,7 @@
         <v>-1.507</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-5.087</v>
+        <v>-5.086</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-1.46</v>
@@ -4159,7 +4157,11 @@
           <t>Current portion of lease obligations 17</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -4323,7 +4325,11 @@
           <t>Lease obligations 17</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -4846,7 +4852,11 @@
           <t>Current portion of lease obligations 16</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -4885,7 +4895,11 @@
           <t>Lease obligations 16</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -5633,7 +5647,11 @@
           <t>Current portion of lease obligations (note 15)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -5838,7 +5856,11 @@
           <t>Lease obligations (note 15)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -6551,7 +6573,11 @@
           <t>Current portion of lease obligations (note 14)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="n">
         <v>0.578</v>
       </c>
@@ -6674,7 +6700,11 @@
           <t>Lease obligations (note 14)</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E79" s="5" t="n">
         <v>1.106</v>
       </c>
@@ -8499,7 +8529,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -9387,7 +9421,11 @@
           <t>Cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
